--- a/results/02_taxa_assemblage/LDA_Method/ModelB_CorePeripheral/artifacts/site_robustness.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelB_CorePeripheral/artifacts/site_robustness.xlsx
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -498,19 +498,19 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5949985296328048</v>
+        <v>0.7549779646997046</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1909785406588097</v>
+        <v>0.2232141722807523</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2140229297083855</v>
+        <v>0.02180786301954313</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5949985296328048</v>
+        <v>0.7549779646997046</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3809755999244192</v>
+        <v>0.5317637924189522</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -533,22 +533,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2651633191622352</v>
+        <v>0.6618228397491238</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1982638606600048</v>
+        <v>0.00525600905422868</v>
       </c>
       <c r="G3" t="n">
-        <v>0.53657282017776</v>
+        <v>0.3329211511966476</v>
       </c>
       <c r="H3" t="n">
-        <v>0.53657282017776</v>
+        <v>0.6618228397491238</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2714095010155248</v>
+        <v>0.3289016885524762</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -563,30 +563,30 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1432129695094798</v>
+        <v>0.6171500216578977</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3579381814661244</v>
+        <v>0.01727928817999209</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4988488490243957</v>
+        <v>0.3655706901621102</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4988488490243957</v>
+        <v>0.6171500216578977</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1409106675582714</v>
+        <v>0.2515793314957874</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -612,19 +612,19 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6583739330518341</v>
+        <v>0.8925015443865257</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04903362239947497</v>
+        <v>0.001392888448577244</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2925924445486909</v>
+        <v>0.1061055671648971</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6583739330518341</v>
+        <v>0.8925015443865257</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3657814885031432</v>
+        <v>0.7863959772216286</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -643,26 +643,26 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08679686443439495</v>
+        <v>0.3112830612792064</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6793072036662459</v>
+        <v>0.6510800661099009</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2338959318993592</v>
+        <v>0.03763687261089275</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6793072036662459</v>
+        <v>0.6510800661099009</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4454112717668867</v>
+        <v>0.3397970048306945</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -688,19 +688,19 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02582836432180469</v>
+        <v>0.01109114251178627</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8931347399965482</v>
+        <v>0.9883305097487155</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08103689568164713</v>
+        <v>0.0005783477394981822</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8931347399965482</v>
+        <v>0.9883305097487155</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8120978443149012</v>
+        <v>0.9772393672369293</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1596257613623493</v>
+        <v>0.6319244694963377</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5521649088718755</v>
+        <v>0.3018787627593236</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2882093297657751</v>
+        <v>0.06619676774433855</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5521649088718755</v>
+        <v>0.6319244694963377</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2639555791061004</v>
+        <v>0.3300457067370141</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -764,19 +764,19 @@
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005816411337875054</v>
+        <v>0.0008544455980962394</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9265482100880885</v>
+        <v>0.9991093822268066</v>
       </c>
       <c r="G9" t="n">
-        <v>0.06763537857403647</v>
+        <v>3.617217509737698e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9265482100880885</v>
+        <v>0.9991093822268066</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8589128315140521</v>
+        <v>0.9982549366287103</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -802,19 +802,19 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08329284479424967</v>
+        <v>0.4542301096407368</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6310771163816598</v>
+        <v>0.4979908041829406</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2856300388240906</v>
+        <v>0.04777908617632246</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6310771163816598</v>
+        <v>0.4979908041829406</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3454470775575691</v>
+        <v>0.04376069454220377</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -840,19 +840,19 @@
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2348456553784846</v>
+        <v>0.4298764090743222</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5403635794827704</v>
+        <v>0.5478353168816952</v>
       </c>
       <c r="G11" t="n">
-        <v>0.224790765138745</v>
+        <v>0.02228827404398263</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5403635794827704</v>
+        <v>0.5478353168816952</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3055179241042857</v>
+        <v>0.117958907807373</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1649756126503208</v>
+        <v>0.08739805159057354</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6918238016796342</v>
+        <v>0.9094452642255231</v>
       </c>
       <c r="G12" t="n">
-        <v>0.143200585670045</v>
+        <v>0.003156684183903366</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6918238016796342</v>
+        <v>0.9094452642255231</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5268481890293134</v>
+        <v>0.8220472126349495</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -905,30 +905,30 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.09360471185791687</v>
+        <v>0.947886244233525</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01499111939960431</v>
+        <v>0.001842106119627295</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8914041687424789</v>
+        <v>0.0502716496468477</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8914041687424789</v>
+        <v>0.947886244233525</v>
       </c>
       <c r="I13" t="n">
-        <v>0.797799456884562</v>
+        <v>0.8976145945866773</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -943,30 +943,30 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1828878323419488</v>
+        <v>0.7378762650907017</v>
       </c>
       <c r="F14" t="n">
-        <v>0.05431701297961558</v>
+        <v>0.001030639319635279</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7627951546784355</v>
+        <v>0.2610930955896629</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7627951546784355</v>
+        <v>0.7378762650907017</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5799073223364868</v>
+        <v>0.4767831695010388</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,22 +989,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1184751581211329</v>
+        <v>0.6955954911963294</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4218655757863208</v>
+        <v>0.09279590434832725</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4596592660925463</v>
+        <v>0.2116086044553434</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4596592660925463</v>
+        <v>0.6955954911963294</v>
       </c>
       <c r="I15" t="n">
-        <v>0.03779369030622548</v>
+        <v>0.483986886740986</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1030,19 +1030,19 @@
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>0.007065714019164181</v>
+        <v>0.0178426796584742</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9337577938568783</v>
+        <v>0.9711104335134431</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05917649212395739</v>
+        <v>0.01104688682808266</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9337577938568783</v>
+        <v>0.9711104335134431</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8745813017329209</v>
+        <v>0.9532677538549689</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1061,26 +1061,26 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>0.04886053823860375</v>
+        <v>0.2960441838771857</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7572271719793739</v>
+        <v>0.5647433699175413</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1939122897820223</v>
+        <v>0.1392124462052729</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7572271719793739</v>
+        <v>0.5647433699175413</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5633148821973517</v>
+        <v>0.2686991860403555</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1106,19 +1106,19 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1609005876873317</v>
+        <v>0.03008278943221596</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6701419751961047</v>
+        <v>0.9691181067856939</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1689574371165635</v>
+        <v>0.000799103782090163</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6701419751961047</v>
+        <v>0.9691181067856939</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5011845380795412</v>
+        <v>0.9390353173534779</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1144,19 +1144,19 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5247605379353433</v>
+        <v>0.8806650594323798</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1076562607444456</v>
+        <v>0.005851423730362198</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3675832013202111</v>
+        <v>0.1134835168372581</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5247605379353433</v>
+        <v>0.8806650594323798</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1571773366151322</v>
+        <v>0.7671815425951217</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>121C</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1182,19 +1182,19 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7165379005921519</v>
+        <v>0.9759847224101345</v>
       </c>
       <c r="F20" t="n">
-        <v>0.07684719035214374</v>
+        <v>0.01243438414780519</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2066149090557043</v>
+        <v>0.01158089344206023</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7165379005921519</v>
+        <v>0.9759847224101345</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5099229915364476</v>
+        <v>0.9635503382623293</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1205,34 +1205,34 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>122B</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1710881819891927</v>
+        <v>0.9345960240540114</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6298466486447568</v>
+        <v>0.01946712958741765</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1990651693660506</v>
+        <v>0.0459368463585708</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6298466486447568</v>
+        <v>0.9345960240540114</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4307814792787062</v>
+        <v>0.8886591776954407</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1243,11 +1243,11 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>125A</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1255,22 +1255,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4289497234883349</v>
+        <v>0.2144574170206051</v>
       </c>
       <c r="F22" t="n">
-        <v>0.07852026325293671</v>
+        <v>0.7745941593649132</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4925300132587284</v>
+        <v>0.01094842361448179</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4925300132587284</v>
+        <v>0.7745941593649132</v>
       </c>
       <c r="I22" t="n">
-        <v>0.06358028977039348</v>
+        <v>0.5601367423443081</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>GL1</t>
+          <t>133B</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1289,26 +1289,26 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2160027351567893</v>
+        <v>0.7048749134979005</v>
       </c>
       <c r="F23" t="n">
-        <v>0.05406866643260889</v>
+        <v>0.015579560155382</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7299285984106019</v>
+        <v>0.2795455263467175</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7299285984106019</v>
+        <v>0.7048749134979005</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5139258632538126</v>
+        <v>0.425329387151183</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>139B</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1334,19 +1334,19 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5611466891467558</v>
+        <v>0.8296355833654192</v>
       </c>
       <c r="F24" t="n">
-        <v>0.07046329065276505</v>
+        <v>0.002511099749325825</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3683900202004792</v>
+        <v>0.167853316885255</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5611466891467558</v>
+        <v>0.8296355833654192</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1927566689462766</v>
+        <v>0.6617822664801642</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1369,22 +1369,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2360244119250482</v>
+        <v>0.6048054475816421</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4063664296592963</v>
+        <v>0.0177156501937663</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3576091584156555</v>
+        <v>0.3774789022245916</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4063664296592963</v>
+        <v>0.6048054475816421</v>
       </c>
       <c r="I25" t="n">
-        <v>0.04875727124364071</v>
+        <v>0.2273265453570505</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1395,11 +1395,11 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1410,19 +1410,19 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5635720586712758</v>
+        <v>0.8661044944409373</v>
       </c>
       <c r="F26" t="n">
-        <v>0.08478968199564774</v>
+        <v>0.002533548098472692</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3516382593330765</v>
+        <v>0.13136195746059</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5635720586712758</v>
+        <v>0.8661044944409373</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2119337993381993</v>
+        <v>0.7347425369803473</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1448,19 +1448,19 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4976868178243005</v>
+        <v>0.8091562416758987</v>
       </c>
       <c r="F27" t="n">
-        <v>0.05265337502190332</v>
+        <v>0.0196454326590326</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4496598071537961</v>
+        <v>0.1711983256650686</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4976868178243005</v>
+        <v>0.8091562416758987</v>
       </c>
       <c r="I27" t="n">
-        <v>0.04802701067050436</v>
+        <v>0.6379579160108302</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1486,19 +1486,19 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6191680064427596</v>
+        <v>0.67217096003495</v>
       </c>
       <c r="F28" t="n">
-        <v>0.06848775186278876</v>
+        <v>0.2697643048105642</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3123442416944517</v>
+        <v>0.0580647351544858</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6191680064427596</v>
+        <v>0.67217096003495</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3068237647483079</v>
+        <v>0.4024066552243858</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1524,19 +1524,19 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8065670218624079</v>
+        <v>0.84213593207301</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01469817121251673</v>
+        <v>0.003636126404369762</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1787348069250754</v>
+        <v>0.1542279415226203</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8065670218624079</v>
+        <v>0.84213593207301</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6278322149373325</v>
+        <v>0.6879079905503896</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1547,11 +1547,11 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>S28(5)</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1562,19 +1562,19 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5318152132359665</v>
+        <v>0.9113983849735523</v>
       </c>
       <c r="F30" t="n">
-        <v>0.02167967416021431</v>
+        <v>0.002276145285916539</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4465051126038194</v>
+        <v>0.08632546974053096</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5318152132359665</v>
+        <v>0.9113983849735523</v>
       </c>
       <c r="I30" t="n">
-        <v>0.08531010063214711</v>
+        <v>0.8250729152330214</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1585,11 +1585,11 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1597,22 +1597,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4614301897899071</v>
+        <v>0.9175504771243086</v>
       </c>
       <c r="F31" t="n">
-        <v>0.05455567400177713</v>
+        <v>0.004657150531607253</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4840141362083158</v>
+        <v>0.07779237234408422</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4840141362083158</v>
+        <v>0.9175504771243086</v>
       </c>
       <c r="I31" t="n">
-        <v>0.02258394641840877</v>
+        <v>0.8397581047802244</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1623,34 +1623,34 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>S28</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5069250079966386</v>
+        <v>0.9827048797501874</v>
       </c>
       <c r="F32" t="n">
-        <v>0.06197761554245805</v>
+        <v>0.002464729253615571</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4310973764609033</v>
+        <v>0.01483039099619709</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5069250079966386</v>
+        <v>0.9827048797501874</v>
       </c>
       <c r="I32" t="n">
-        <v>0.07582763153573535</v>
+        <v>0.9678744887539903</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S28(5)</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1669,26 +1669,26 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>0.580089823535113</v>
+        <v>0.7371473913958311</v>
       </c>
       <c r="F33" t="n">
-        <v>0.06272480178297511</v>
+        <v>4.382006134879314e-05</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3571853746819119</v>
+        <v>0.2628087885428201</v>
       </c>
       <c r="H33" t="n">
-        <v>0.580089823535113</v>
+        <v>0.7371473913958311</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2229044488532011</v>
+        <v>0.474338602853011</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1699,11 +1699,11 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1714,19 +1714,19 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4667563513825961</v>
+        <v>0.7727472139541769</v>
       </c>
       <c r="F34" t="n">
-        <v>0.08729703010374729</v>
+        <v>0.0005899545448246134</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4459466185136566</v>
+        <v>0.2266628315009987</v>
       </c>
       <c r="H34" t="n">
-        <v>0.4667563513825961</v>
+        <v>0.7727472139541769</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0208097328689395</v>
+        <v>0.5460843824531783</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1737,11 +1737,11 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>S50</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1749,22 +1749,22 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3521010194507085</v>
+        <v>0.7958327839643894</v>
       </c>
       <c r="F35" t="n">
-        <v>0.08637729687605138</v>
+        <v>0.000974049066607456</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5615216836732401</v>
+        <v>0.2031931669690031</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5615216836732401</v>
+        <v>0.7958327839643894</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2094206642225316</v>
+        <v>0.5926396169953863</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1783,26 +1783,26 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6022464835372026</v>
+        <v>0.7748885524660708</v>
       </c>
       <c r="F36" t="n">
-        <v>0.05622028480049232</v>
+        <v>0.000849144307862603</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3415332316623052</v>
+        <v>0.2242623032260667</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6022464835372026</v>
+        <v>0.7748885524660708</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2607132518748974</v>
+        <v>0.550626249240004</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1813,11 +1813,11 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1825,22 +1825,22 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2879463294962945</v>
+        <v>0.7209558815693512</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2675079122769882</v>
+        <v>0.0008894939034777275</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4445457582267173</v>
+        <v>0.2781546245271711</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4445457582267173</v>
+        <v>0.7209558815693512</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1565994287304229</v>
+        <v>0.4428012570421801</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S50</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1859,26 +1859,26 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4157999450560583</v>
+        <v>0.8129240107516708</v>
       </c>
       <c r="F38" t="n">
-        <v>0.08916697793615393</v>
+        <v>0.002410800069952336</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4950330770077877</v>
+        <v>0.1846651891783768</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4950330770077877</v>
+        <v>0.8129240107516708</v>
       </c>
       <c r="I38" t="n">
-        <v>0.07923313195172943</v>
+        <v>0.6282588215732939</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -1889,34 +1889,34 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S51</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3066771247883693</v>
+        <v>0.7903801033358235</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2433881365836267</v>
+        <v>0.0007908391855481508</v>
       </c>
       <c r="G39" t="n">
-        <v>0.449934738628004</v>
+        <v>0.2088290574786284</v>
       </c>
       <c r="H39" t="n">
-        <v>0.449934738628004</v>
+        <v>0.7903801033358235</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1432576138396348</v>
+        <v>0.5815510458571951</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -1927,34 +1927,34 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>S65</t>
+          <t>S52</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>0.555668141646107</v>
+        <v>0.6801123487241238</v>
       </c>
       <c r="F40" t="n">
-        <v>0.06885540293886691</v>
+        <v>0.01005377423255643</v>
       </c>
       <c r="G40" t="n">
-        <v>0.3754764554150261</v>
+        <v>0.3098338770433197</v>
       </c>
       <c r="H40" t="n">
-        <v>0.555668141646107</v>
+        <v>0.6801123487241238</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1801916862310809</v>
+        <v>0.3702784716808041</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>S69</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1977,22 +1977,22 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2813059165474168</v>
+        <v>0.5082132303277805</v>
       </c>
       <c r="F41" t="n">
-        <v>0.06864335198980148</v>
+        <v>0.0002573350930629661</v>
       </c>
       <c r="G41" t="n">
-        <v>0.6500507314627816</v>
+        <v>0.4915294345791564</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6500507314627816</v>
+        <v>0.5082132303277805</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3687448149153648</v>
+        <v>0.01668379574862411</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2003,11 +2003,11 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>S70</t>
+          <t>S65</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2015,22 +2015,22 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2136247707255321</v>
+        <v>0.7799293646860298</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3822784591009425</v>
+        <v>0.0009935597457388474</v>
       </c>
       <c r="G42" t="n">
-        <v>0.4040967701735254</v>
+        <v>0.2190770755682313</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4040967701735254</v>
+        <v>0.7799293646860298</v>
       </c>
       <c r="I42" t="n">
-        <v>0.02181831107258286</v>
+        <v>0.5608522891177985</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2041,34 +2041,34 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>S72</t>
+          <t>S69</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1812931000986273</v>
+        <v>0.5447148810150164</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3148495772612373</v>
+        <v>0.000255215868638442</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5038573226401355</v>
+        <v>0.4550299031163452</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5038573226401355</v>
+        <v>0.5447148810150164</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1890077453788982</v>
+        <v>0.08968497789867125</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>S79</t>
+          <t>S70</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2087,26 +2087,26 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3810865897534437</v>
+        <v>0.639378787935898</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2194553777079356</v>
+        <v>0.02982768684107812</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3994580325386208</v>
+        <v>0.330793525223024</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3994580325386208</v>
+        <v>0.639378787935898</v>
       </c>
       <c r="I44" t="n">
-        <v>0.01837144278517716</v>
+        <v>0.308585262712874</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2117,34 +2117,34 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S72</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D45" t="n">
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4731655810720934</v>
+        <v>0.5138938348130593</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1056497942504016</v>
+        <v>0.01039917345797956</v>
       </c>
       <c r="G45" t="n">
-        <v>0.4211846246775051</v>
+        <v>0.4757069917289611</v>
       </c>
       <c r="H45" t="n">
-        <v>0.4731655810720934</v>
+        <v>0.5138938348130593</v>
       </c>
       <c r="I45" t="n">
-        <v>0.05198095639458827</v>
+        <v>0.03818684308409814</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>S81</t>
+          <t>S74</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -2163,26 +2163,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
       <c r="D46" t="n">
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4253764540101057</v>
+        <v>0.7527699022283815</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2876849964446677</v>
+        <v>0.01252478408421505</v>
       </c>
       <c r="G46" t="n">
-        <v>0.2869385495452268</v>
+        <v>0.2347053136874033</v>
       </c>
       <c r="H46" t="n">
-        <v>0.4253764540101057</v>
+        <v>0.7527699022283815</v>
       </c>
       <c r="I46" t="n">
-        <v>0.137691457565438</v>
+        <v>0.5180645885409783</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>S79</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -2201,37 +2201,37 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D47" t="n">
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>0.6917609145661818</v>
+        <v>0.8423713775849021</v>
       </c>
       <c r="F47" t="n">
-        <v>0.04319565258779271</v>
+        <v>0.02785063814372586</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2650434328460256</v>
+        <v>0.129777984271372</v>
       </c>
       <c r="H47" t="n">
-        <v>0.6917609145661818</v>
+        <v>0.8423713775849021</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4267174817201563</v>
+        <v>0.7125933933135301</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Held-out</t>
+          <t>Train</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -2239,79 +2239,79 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2687837263580748</v>
+        <v>0.8083010097910375</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2090586258329865</v>
+        <v>0.002936220330340001</v>
       </c>
       <c r="G48" t="n">
-        <v>0.5221576478089386</v>
+        <v>0.1887627698786225</v>
       </c>
       <c r="H48" t="n">
-        <v>0.5221576478089386</v>
+        <v>0.8083010097910375</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2533739214508637</v>
+        <v>0.619538239912415</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Held-out</t>
+          <t>Train</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S81</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Core</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2329014762378219</v>
+        <v>0.7145253893522687</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3695141408736883</v>
+        <v>0.2191941810731493</v>
       </c>
       <c r="G49" t="n">
-        <v>0.3975843828884897</v>
+        <v>0.06628042957458186</v>
       </c>
       <c r="H49" t="n">
-        <v>0.3975843828884897</v>
+        <v>0.7145253893522687</v>
       </c>
       <c r="I49" t="n">
-        <v>0.02807024201480135</v>
+        <v>0.4953312082791194</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Held-out</t>
+          <t>Train</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>GL1</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2322,19 +2322,19 @@
         <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>0.3094747352598711</v>
+        <v>0.1443578916117968</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2158256894385251</v>
+        <v>4.085099451682151e-06</v>
       </c>
       <c r="G50" t="n">
-        <v>0.4746995753016038</v>
+        <v>0.8556380232887515</v>
       </c>
       <c r="H50" t="n">
-        <v>0.4746995753016038</v>
+        <v>0.8556380232887515</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1652248400417327</v>
+        <v>0.7112801316769547</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2345,11 +2345,11 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>S74</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2357,22 +2357,22 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>0.2562442585369242</v>
+        <v>0.6461985272366956</v>
       </c>
       <c r="F51" t="n">
-        <v>0.239365821992594</v>
+        <v>0.005331938135341549</v>
       </c>
       <c r="G51" t="n">
-        <v>0.5043899194704818</v>
+        <v>0.3484695346279628</v>
       </c>
       <c r="H51" t="n">
-        <v>0.5043899194704818</v>
+        <v>0.6461985272366956</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2481456609335577</v>
+        <v>0.2977289926087328</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
